--- a/SMI-Excels/VUC/template_G2-S2.xlsx
+++ b/SMI-Excels/VUC/template_G2-S2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011" filterPrivacy="true"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -397,37 +397,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:AF2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>vuc_id</v>
+        <v>vucId</v>
       </c>
       <c r="B1" t="str">
-        <v>declaration_type</v>
+        <v>declarationType</v>
       </c>
       <c r="C1" t="str">
-        <v>year_declaration</v>
+        <v>yearDeclaration</v>
       </c>
       <c r="D1" t="str">
-        <v>group_type</v>
+        <v>groupType</v>
       </c>
       <c r="E1" t="str">
-        <v>depositors_count</v>
+        <v>depositorId</v>
       </c>
       <c r="F1" t="str">
-        <v>Detail.depositor_id</v>
+        <v>actionType</v>
       </c>
       <c r="G1" t="str">
-        <v>Detail.action_type</v>
+        <v>personType</v>
       </c>
       <c r="H1" t="str">
-        <v>Detail.person_type</v>
+        <v>firstName</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lastName</v>
+      </c>
+      <c r="J1" t="str">
+        <v>cinNum</v>
+      </c>
+      <c r="K1" t="str">
+        <v>companyName</v>
+      </c>
+      <c r="L1" t="str">
+        <v>rne</v>
+      </c>
+      <c r="M1" t="str">
+        <v>accountsCount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>accountNumber</v>
+      </c>
+      <c r="O1" t="str">
+        <v>commercialName</v>
+      </c>
+      <c r="P1" t="str">
+        <v>accountTitle</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>accountNature</v>
+      </c>
+      <c r="R1" t="str">
+        <v>holdersCount</v>
+      </c>
+      <c r="S1" t="str">
+        <v>accountBalance</v>
+      </c>
+      <c r="T1" t="str">
+        <v>compensableAggregateBalance</v>
+      </c>
+      <c r="U1" t="str">
+        <v>vucIdCoAccountHolders</v>
+      </c>
+      <c r="V1" t="str">
+        <v>currency</v>
+      </c>
+      <c r="W1" t="str">
+        <v>accountBusinessName</v>
+      </c>
+      <c r="X1" t="str">
+        <v>accountStatus</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>debitAccountBalance</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>creditAccountBalance</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>totalOverdueUnpaidDebts</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>totalDeferredDebits</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>totalAgios</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>totalGuaranteeUnreleased</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>totalInterest</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>totalDeductions</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>111</v>
+      </c>
+      <c r="B2">
+        <v>1111</v>
+      </c>
+      <c r="C2">
+        <v>1111</v>
+      </c>
+      <c r="D2">
+        <v>1111</v>
+      </c>
+      <c r="E2">
+        <v>1111</v>
+      </c>
+      <c r="F2">
+        <v>11111</v>
+      </c>
+      <c r="G2">
+        <v>11111</v>
+      </c>
+      <c r="H2">
+        <v>11111</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF2"/>
   </ignoredErrors>
 </worksheet>
 </file>